--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\45087114\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000951B3-6058-C746-846C-8734C2463E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D3815B-E818-4BCD-92C0-1D93CE5BDE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Documento</t>
   </si>
@@ -173,6 +173,36 @@
   </si>
   <si>
     <t>Carlos Emilio Riascos Angulo</t>
+  </si>
+  <si>
+    <t>Mirian Herrera Lucero</t>
+  </si>
+  <si>
+    <t>Betzy Danitza Medina Pereyra</t>
+  </si>
+  <si>
+    <t>08886630</t>
+  </si>
+  <si>
+    <t>Alexi John Mimbela Hinojosa</t>
+  </si>
+  <si>
+    <t>Gracia Cristina Alejandra Fernández Mejía</t>
+  </si>
+  <si>
+    <t>Cristina Medina Casapaico</t>
+  </si>
+  <si>
+    <t>07507292</t>
+  </si>
+  <si>
+    <t>Geraldine Consuelo Vargas Machuca Fajardo</t>
+  </si>
+  <si>
+    <t>Maria Cristina Palacios Ñuflo</t>
+  </si>
+  <si>
+    <t>Rosa Jazmin Vásquez Huaman</t>
   </si>
 </sst>
 </file>
@@ -258,7 +288,97 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -719,14 +839,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -734,7 +854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1069832679</v>
       </c>
@@ -742,7 +862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1110538315</v>
       </c>
@@ -750,7 +870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1024591972</v>
       </c>
@@ -758,7 +878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1007719161</v>
       </c>
@@ -766,7 +886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1022415180</v>
       </c>
@@ -774,7 +894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1007437362</v>
       </c>
@@ -782,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>52360965</v>
       </c>
@@ -790,7 +910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>52359520</v>
       </c>
@@ -798,7 +918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1033685058</v>
       </c>
@@ -806,7 +926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>1043663400</v>
       </c>
@@ -814,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1064556081</v>
       </c>
@@ -822,7 +942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1024574799</v>
       </c>
@@ -830,7 +950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1023866590</v>
       </c>
@@ -838,7 +958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1069750848</v>
       </c>
@@ -846,7 +966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>52937353</v>
       </c>
@@ -854,7 +974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>33223712</v>
       </c>
@@ -862,7 +982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1006854586</v>
       </c>
@@ -870,7 +990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>1010207469</v>
       </c>
@@ -878,7 +998,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1030678228</v>
       </c>
@@ -886,7 +1006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1032677600</v>
       </c>
@@ -894,7 +1014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1000784663</v>
       </c>
@@ -902,7 +1022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>1006126137</v>
       </c>
@@ -910,7 +1030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1010231249</v>
       </c>
@@ -918,7 +1038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>1022399552</v>
       </c>
@@ -926,7 +1046,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>1000873002</v>
       </c>
@@ -934,7 +1054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>1128277446</v>
       </c>
@@ -942,7 +1062,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>1000635646</v>
       </c>
@@ -950,7 +1070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>1030680116</v>
       </c>
@@ -958,7 +1078,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>1035230632</v>
       </c>
@@ -966,7 +1086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>1128450311</v>
       </c>
@@ -974,7 +1094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>43482107</v>
       </c>
@@ -982,7 +1102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>43182389</v>
       </c>
@@ -990,7 +1110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>1035416124</v>
       </c>
@@ -998,7 +1118,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>1096256836</v>
       </c>
@@ -1006,7 +1126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>71311840</v>
       </c>
@@ -1014,7 +1134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>1020103943</v>
       </c>
@@ -1022,7 +1142,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>1007253252</v>
       </c>
@@ -1030,7 +1150,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>1000406210</v>
       </c>
@@ -1038,7 +1158,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>1001138890</v>
       </c>
@@ -1046,7 +1166,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>1214729990</v>
       </c>
@@ -1054,7 +1174,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>1010213899</v>
       </c>
@@ -1062,7 +1182,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>1232399996</v>
       </c>
@@ -1070,7 +1190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>1001299432</v>
       </c>
@@ -1078,7 +1198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>1006187617</v>
       </c>
@@ -1086,31 +1206,114 @@
         <v>45</v>
       </c>
     </row>
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>60399217</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>43067936</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>60856457</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>47096365</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>74712540</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>77338419</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A45">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
+  <conditionalFormatting sqref="A17:A53">
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A45">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="A26:A53">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:B38 A36:A37">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\45087114\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D3815B-E818-4BCD-92C0-1D93CE5BDE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AACC4E-CF74-9647-82AE-7684CA2C4110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Documento</t>
   </si>
@@ -175,34 +175,22 @@
     <t>Carlos Emilio Riascos Angulo</t>
   </si>
   <si>
-    <t>Mirian Herrera Lucero</t>
-  </si>
-  <si>
-    <t>Betzy Danitza Medina Pereyra</t>
-  </si>
-  <si>
-    <t>08886630</t>
-  </si>
-  <si>
-    <t>Alexi John Mimbela Hinojosa</t>
-  </si>
-  <si>
-    <t>Gracia Cristina Alejandra Fernández Mejía</t>
-  </si>
-  <si>
-    <t>Cristina Medina Casapaico</t>
-  </si>
-  <si>
-    <t>07507292</t>
-  </si>
-  <si>
-    <t>Geraldine Consuelo Vargas Machuca Fajardo</t>
-  </si>
-  <si>
-    <t>Maria Cristina Palacios Ñuflo</t>
-  </si>
-  <si>
-    <t>Rosa Jazmin Vásquez Huaman</t>
+    <t>Carlos Ulises Hidalgo Arrieta</t>
+  </si>
+  <si>
+    <t>Milagros Velasquez Yahuacani</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ana Pilar Rosales Hermoza</t>
+  </si>
+  <si>
+    <t>Gracia Cristina Alejandra Fernandez</t>
+  </si>
+  <si>
+    <t>77337419</t>
+  </si>
+  <si>
+    <t>Rosa Jazmin Vasquez</t>
   </si>
 </sst>
 </file>
@@ -288,97 +276,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -839,14 +737,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1069832679</v>
       </c>
@@ -862,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1110538315</v>
       </c>
@@ -870,7 +768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1024591972</v>
       </c>
@@ -878,7 +776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1007719161</v>
       </c>
@@ -886,7 +784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1022415180</v>
       </c>
@@ -894,7 +792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>1007437362</v>
       </c>
@@ -902,7 +800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>52360965</v>
       </c>
@@ -910,7 +808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>52359520</v>
       </c>
@@ -918,7 +816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1033685058</v>
       </c>
@@ -926,7 +824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1043663400</v>
       </c>
@@ -934,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1064556081</v>
       </c>
@@ -942,7 +840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1024574799</v>
       </c>
@@ -950,7 +848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1023866590</v>
       </c>
@@ -958,7 +856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1069750848</v>
       </c>
@@ -966,7 +864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>52937353</v>
       </c>
@@ -974,7 +872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>33223712</v>
       </c>
@@ -982,7 +880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1006854586</v>
       </c>
@@ -990,7 +888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1010207469</v>
       </c>
@@ -998,7 +896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1030678228</v>
       </c>
@@ -1006,7 +904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>1032677600</v>
       </c>
@@ -1014,7 +912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1000784663</v>
       </c>
@@ -1022,7 +920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1006126137</v>
       </c>
@@ -1030,7 +928,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1010231249</v>
       </c>
@@ -1038,7 +936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1022399552</v>
       </c>
@@ -1046,7 +944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>1000873002</v>
       </c>
@@ -1054,7 +952,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>1128277446</v>
       </c>
@@ -1062,7 +960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1000635646</v>
       </c>
@@ -1070,7 +968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1030680116</v>
       </c>
@@ -1078,7 +976,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1035230632</v>
       </c>
@@ -1086,7 +984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1128450311</v>
       </c>
@@ -1094,7 +992,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>43482107</v>
       </c>
@@ -1102,7 +1000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>43182389</v>
       </c>
@@ -1110,7 +1008,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1035416124</v>
       </c>
@@ -1118,7 +1016,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1096256836</v>
       </c>
@@ -1126,7 +1024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>71311840</v>
       </c>
@@ -1134,7 +1032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1020103943</v>
       </c>
@@ -1142,7 +1040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1007253252</v>
       </c>
@@ -1150,7 +1048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1000406210</v>
       </c>
@@ -1158,7 +1056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1001138890</v>
       </c>
@@ -1166,7 +1064,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1214729990</v>
       </c>
@@ -1174,7 +1072,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1010213899</v>
       </c>
@@ -1182,7 +1080,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1232399996</v>
       </c>
@@ -1190,7 +1088,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1001299432</v>
       </c>
@@ -1198,7 +1096,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1006187617</v>
       </c>
@@ -1206,114 +1104,71 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>60399217</v>
+        <v>7215509</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>76566719</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>43067936</v>
-      </c>
-      <c r="B47" s="3" t="s">
+    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>77377356</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>60856457</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>47096365</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>74712540</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>77338419</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A53">
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+  <conditionalFormatting sqref="A17:A50">
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A53">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  <conditionalFormatting sqref="A26:A50">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:B38 A36:A37">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AACC4E-CF74-9647-82AE-7684CA2C4110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045B2889-767A-4F49-A4DD-8FFD9378E3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Documento</t>
   </si>
@@ -121,48 +121,18 @@
     <t>Laura Inés Sánchez Velásquez</t>
   </si>
   <si>
-    <t>Yuli Tatiana Marin Rondon</t>
-  </si>
-  <si>
-    <t>Maidy Yineth Fernandez Fernandez</t>
-  </si>
-  <si>
     <t>Daniel Mestre Suescun</t>
   </si>
   <si>
     <t>Liliana Maria Bogota Navarro</t>
   </si>
   <si>
-    <t>Girlesa Eugenia Monsalve Castro</t>
-  </si>
-  <si>
     <t>Ana María guerra Álvarez</t>
   </si>
   <si>
-    <t>Gustavo Adolfo Zea Valencia</t>
-  </si>
-  <si>
-    <t>Fernando Alonso García Urbaneja</t>
-  </si>
-  <si>
-    <t>Carlos Andres Mojica Betancur</t>
-  </si>
-  <si>
-    <t>Alejandro Cardona Rueda</t>
-  </si>
-  <si>
-    <t>Mildrey Cano Loaiza</t>
-  </si>
-  <si>
     <t>Santiago Argumedo Montoya</t>
   </si>
   <si>
-    <t>Valeria Suárez Cuartas</t>
-  </si>
-  <si>
-    <t>Jose Andres Toro Correa</t>
-  </si>
-  <si>
     <t>Paula Andrea Martínez Neira</t>
   </si>
   <si>
@@ -191,6 +161,66 @@
   </si>
   <si>
     <t>Rosa Jazmin Vasquez</t>
+  </si>
+  <si>
+    <t>Jaime Andres Baron Guerrero</t>
+  </si>
+  <si>
+    <t>Karen Dayana Rincon Ortiz</t>
+  </si>
+  <si>
+    <t>Karen Hasbleidy Molina Baquero</t>
+  </si>
+  <si>
+    <t>Leidy Tatiana Rodriguez Chaves</t>
+  </si>
+  <si>
+    <t>Manuel Leonardo Galeano Fontecha</t>
+  </si>
+  <si>
+    <t>Roseily Maria Ruiz Castillo</t>
+  </si>
+  <si>
+    <t>Tatiana Alejandra Calderon Cantor</t>
+  </si>
+  <si>
+    <t>Jeimy Alejandra Fajardo Hurtado</t>
+  </si>
+  <si>
+    <t>Maryuri Disney Solano Gomez</t>
+  </si>
+  <si>
+    <t>Johanna Paola Rodriguez Castano</t>
+  </si>
+  <si>
+    <t>Juan Carlos Vasquez Guerrero</t>
+  </si>
+  <si>
+    <t>Maria Angelica Castilla Bernal</t>
+  </si>
+  <si>
+    <t>Dilan Esteban Ballen Gualdron</t>
+  </si>
+  <si>
+    <t>Manuel Felipe Romero Huerfano</t>
+  </si>
+  <si>
+    <t>Andrea Marcela Dias Barrero</t>
+  </si>
+  <si>
+    <t>Brandon Yesid Florez Peinado</t>
+  </si>
+  <si>
+    <t>Robert Nicolas Arnedo Socadagui</t>
+  </si>
+  <si>
+    <t>William Camilo Torres Lopez</t>
+  </si>
+  <si>
+    <t>Dana Julieth Patino Malagon</t>
+  </si>
+  <si>
+    <t>Paula Andrea Molina Carrillo</t>
   </si>
 </sst>
 </file>
@@ -276,23 +306,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -737,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -962,7 +982,7 @@
     </row>
     <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1000635646</v>
+        <v>1035230632</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>28</v>
@@ -970,7 +990,7 @@
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1030680116</v>
+        <v>1128450311</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -978,7 +998,7 @@
     </row>
     <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1035230632</v>
+        <v>43182389</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>30</v>
@@ -986,7 +1006,7 @@
     </row>
     <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1128450311</v>
+        <v>1000406210</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -994,7 +1014,7 @@
     </row>
     <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>43482107</v>
+        <v>1010213899</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>32</v>
@@ -1002,7 +1022,7 @@
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>43182389</v>
+        <v>1232399996</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>33</v>
@@ -1010,7 +1030,7 @@
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1035416124</v>
+        <v>1001299432</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>34</v>
@@ -1018,7 +1038,7 @@
     </row>
     <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1096256836</v>
+        <v>1006187617</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>35</v>
@@ -1026,149 +1046,228 @@
     </row>
     <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>71311840</v>
+        <v>7215509</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>1020103943</v>
+        <v>76566719</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1007253252</v>
+        <v>77377356</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1000406210</v>
+        <v>60856457</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>1001138890</v>
+      <c r="A40" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1214729990</v>
+        <v>1026269702</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1010213899</v>
+        <v>1000268963</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1232399996</v>
+        <v>1030687904</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1001299432</v>
+        <v>1012428710</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1006187617</v>
+        <v>13958754</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>7215509</v>
+        <v>5115859</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>76566719</v>
+        <v>1000048809</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>77377356</v>
+        <v>1023026833</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>60856457</v>
+        <v>1022973517</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>50</v>
+      <c r="A50" s="2">
+        <v>1022328197</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>1016019099</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>1033716719</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>1073671678</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>1030595790</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>1031135783</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>1005180052</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>1013677430</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>1032796079</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>1000691794</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>1023365940</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
     <cfRule type="duplicateValues" dxfId="10" priority="8"/>
     <cfRule type="duplicateValues" dxfId="9" priority="9"/>
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
     <cfRule type="duplicateValues" dxfId="7" priority="11"/>
     <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A50">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
+  <conditionalFormatting sqref="A17:A40">
+    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A50">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="A26:A40">
+    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:B38 A36:A37">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A41:A60">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045B2889-767A-4F49-A4DD-8FFD9378E3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924B1AF6-819B-124C-9C1D-23F43A6B2B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$60</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -157,9 +160,6 @@
     <t>Gracia Cristina Alejandra Fernandez</t>
   </si>
   <si>
-    <t>77337419</t>
-  </si>
-  <si>
     <t>Rosa Jazmin Vasquez</t>
   </si>
   <si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Paula Andrea Molina Carrillo</t>
+  </si>
+  <si>
+    <t>77338419</t>
   </si>
 </sst>
 </file>
@@ -312,7 +315,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -322,7 +325,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -774,50 +777,50 @@
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1069832679</v>
+        <v>5115859</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>1110538315</v>
+        <v>7215509</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1024591972</v>
+        <v>13958754</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1007719161</v>
+        <v>33223712</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>1022415180</v>
+        <v>43182389</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>1007437362</v>
+        <v>52359520</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -830,258 +833,258 @@
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>52359520</v>
+        <v>52937353</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>1033685058</v>
+        <v>60856457</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>1043663400</v>
+        <v>76566719</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>1064556081</v>
+        <v>77377356</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>1024574799</v>
+        <v>1000048809</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>1023866590</v>
+        <v>1000268963</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>1069750848</v>
+        <v>1000406210</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>52937353</v>
+        <v>1000691794</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>33223712</v>
+        <v>1000784663</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>1006854586</v>
+        <v>1000873002</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>1010207469</v>
+        <v>1001299432</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>1030678228</v>
+        <v>1005180052</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>1032677600</v>
+        <v>1006126137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>1000784663</v>
+        <v>1006187617</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>1006126137</v>
+        <v>1006854586</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>1010231249</v>
+        <v>1007437362</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>1022399552</v>
+        <v>1007719161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>1000873002</v>
+        <v>1010207469</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>1128277446</v>
+        <v>1010213899</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1035230632</v>
+        <v>1010231249</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1128450311</v>
+        <v>1012428710</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>43182389</v>
+        <v>1013677430</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1000406210</v>
+        <v>1016019099</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>1010213899</v>
+        <v>1022328197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>1232399996</v>
+        <v>1022399552</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1001299432</v>
+        <v>1022415180</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1006187617</v>
+        <v>1022973517</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>7215509</v>
+        <v>1023026833</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>76566719</v>
+        <v>1023365940</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>77377356</v>
+        <v>1023866590</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>60856457</v>
+        <v>1024574799</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>40</v>
+      <c r="A40" s="2">
+        <v>1024591972</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -1089,186 +1092,188 @@
         <v>1026269702</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1000268963</v>
+        <v>1030595790</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1030687904</v>
+        <v>1030678228</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1012428710</v>
+        <v>1030687904</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>13958754</v>
+        <v>1031135783</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>5115859</v>
+        <v>1032677600</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1000048809</v>
+        <v>1032796079</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1023026833</v>
+        <v>1033685058</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1022973517</v>
+        <v>1033716719</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1022328197</v>
+        <v>1035230632</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1016019099</v>
+        <v>1043663400</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1033716719</v>
+        <v>1064556081</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>1073671678</v>
+        <v>1069750848</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>1030595790</v>
+        <v>1069832679</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>1031135783</v>
+        <v>1073671678</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>1005180052</v>
+        <v>1110538315</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>1013677430</v>
+        <v>1128277446</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>1032796079</v>
+        <v>1128450311</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>1000691794</v>
+        <v>1232399996</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>1023365940</v>
+      <c r="A60" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
-  </conditionalFormatting>
+  <autoFilter ref="A1:B60" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}"/>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A40">
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:A40">
-    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:A60">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A60">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924B1AF6-819B-124C-9C1D-23F43A6B2B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EA26A9B-2425-9943-912B-697C6C2C385E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16100" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Documento</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Carlos Ulises Hidalgo Arrieta</t>
   </si>
   <si>
-    <t>Milagros Velasquez Yahuacani</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Ana Pilar Rosales Hermoza</t>
   </si>
   <si>
@@ -224,6 +221,36 @@
   </si>
   <si>
     <t>77338419</t>
+  </si>
+  <si>
+    <t>Jose Armando Leon Porras</t>
+  </si>
+  <si>
+    <t>Edben Gerardo Calla Crispin</t>
+  </si>
+  <si>
+    <t>Katherine Rebeca Morey Minaya</t>
+  </si>
+  <si>
+    <t>Anthony Miguel Accilio Rojas</t>
+  </si>
+  <si>
+    <t>Jerson Jesus Cardenas Flores</t>
+  </si>
+  <si>
+    <t>Gabriela Pacahuala Mau</t>
+  </si>
+  <si>
+    <t>Jeam Framco Anselmo Leon</t>
+  </si>
+  <si>
+    <t>María Alejandra Lopez Acosta</t>
+  </si>
+  <si>
+    <t>Verónica Carrasco Suárez</t>
+  </si>
+  <si>
+    <t>Dalia Avalos Rojas</t>
   </si>
 </sst>
 </file>
@@ -760,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -780,7 +807,7 @@
         <v>5115859</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -788,7 +815,7 @@
         <v>7215509</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -796,7 +823,7 @@
         <v>13958754</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -844,7 +871,7 @@
         <v>60856457</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -857,398 +884,470 @@
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>77377356</v>
+        <v>1000048809</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>1000048809</v>
+        <v>1000268963</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>1000268963</v>
+        <v>1000406210</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>1000406210</v>
+        <v>1000691794</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>1000691794</v>
+        <v>1000784663</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>1000784663</v>
+        <v>1000873002</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>1000873002</v>
+        <v>1001299432</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>1001299432</v>
+        <v>1005180052</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>1005180052</v>
+        <v>1006126137</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>1006126137</v>
+        <v>1006187617</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>1006187617</v>
+        <v>1006854586</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>1006854586</v>
+        <v>1007437362</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>1007437362</v>
+        <v>1007719161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>1007719161</v>
+        <v>1010207469</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>1010207469</v>
+        <v>1010213899</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>1010213899</v>
+        <v>1010231249</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1010231249</v>
+        <v>1012428710</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1012428710</v>
+        <v>1013677430</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1013677430</v>
+        <v>1016019099</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1016019099</v>
+        <v>1022328197</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>1022328197</v>
+        <v>1022399552</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>1022399552</v>
+        <v>1022415180</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1022415180</v>
+        <v>1022973517</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1022973517</v>
+        <v>1023026833</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>1023026833</v>
+        <v>1023365940</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>1023365940</v>
+        <v>1023866590</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1023866590</v>
+        <v>1024574799</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1024574799</v>
+        <v>1024591972</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>1024591972</v>
+        <v>1026269702</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1026269702</v>
+        <v>1030595790</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1030595790</v>
+        <v>1030678228</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1030678228</v>
+        <v>1030687904</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1030687904</v>
+        <v>1031135783</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1031135783</v>
+        <v>1032677600</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>1032677600</v>
+        <v>1032796079</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1032796079</v>
+        <v>1033685058</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1033685058</v>
+        <v>1033716719</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1033716719</v>
+        <v>1035230632</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1035230632</v>
+        <v>1043663400</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1043663400</v>
+        <v>1064556081</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1064556081</v>
+        <v>1069750848</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>1069750848</v>
+        <v>1069832679</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>1069832679</v>
+        <v>1073671678</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>1073671678</v>
+        <v>1110538315</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>1110538315</v>
+        <v>1128277446</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>1128277446</v>
+        <v>1128450311</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>1128450311</v>
+        <v>1232399996</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="2">
-        <v>1232399996</v>
+      <c r="A59" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="2">
+        <v>70634903</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>40</v>
+    </row>
+    <row r="61" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>41966389</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>9011527</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>74584166</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>61034044</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>46437661</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>76926152</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>7850201</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>9599394</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>41062576</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B60" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}"/>
+  <autoFilter ref="A1:B59" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}"/>
   <conditionalFormatting sqref="A9">
     <cfRule type="duplicateValues" dxfId="11" priority="8"/>
     <cfRule type="duplicateValues" dxfId="10" priority="9"/>
@@ -1257,21 +1356,21 @@
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
     <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A16">
+  <conditionalFormatting sqref="A14:A15">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A40">
+  <conditionalFormatting sqref="A16:A39">
     <cfRule type="duplicateValues" dxfId="4" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A40">
+  <conditionalFormatting sqref="A25:A39">
     <cfRule type="duplicateValues" dxfId="3" priority="35"/>
     <cfRule type="duplicateValues" dxfId="2" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41:A60">
+  <conditionalFormatting sqref="A40:A69">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A60">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  <conditionalFormatting sqref="A2:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EA26A9B-2425-9943-912B-697C6C2C385E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814C4A94-2EB8-8B4D-9B81-C2F6577B5A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16100" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>Documento</t>
   </si>
@@ -251,6 +251,210 @@
   </si>
   <si>
     <t>Dalia Avalos Rojas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>5115859</t>
+  </si>
+  <si>
+    <t>7215509</t>
+  </si>
+  <si>
+    <t>13958754</t>
+  </si>
+  <si>
+    <t>33223712</t>
+  </si>
+  <si>
+    <t>43182389</t>
+  </si>
+  <si>
+    <t>52359520</t>
+  </si>
+  <si>
+    <t>52360965</t>
+  </si>
+  <si>
+    <t>52937353</t>
+  </si>
+  <si>
+    <t>60856457</t>
+  </si>
+  <si>
+    <t>76566719</t>
+  </si>
+  <si>
+    <t>1000048809</t>
+  </si>
+  <si>
+    <t>1000268963</t>
+  </si>
+  <si>
+    <t>1000406210</t>
+  </si>
+  <si>
+    <t>1000691794</t>
+  </si>
+  <si>
+    <t>1000784663</t>
+  </si>
+  <si>
+    <t>1000873002</t>
+  </si>
+  <si>
+    <t>1001299432</t>
+  </si>
+  <si>
+    <t>1005180052</t>
+  </si>
+  <si>
+    <t>1006126137</t>
+  </si>
+  <si>
+    <t>1006187617</t>
+  </si>
+  <si>
+    <t>1006854586</t>
+  </si>
+  <si>
+    <t>1007437362</t>
+  </si>
+  <si>
+    <t>1007719161</t>
+  </si>
+  <si>
+    <t>1010207469</t>
+  </si>
+  <si>
+    <t>1010213899</t>
+  </si>
+  <si>
+    <t>1010231249</t>
+  </si>
+  <si>
+    <t>1012428710</t>
+  </si>
+  <si>
+    <t>1013677430</t>
+  </si>
+  <si>
+    <t>1016019099</t>
+  </si>
+  <si>
+    <t>1022328197</t>
+  </si>
+  <si>
+    <t>1022399552</t>
+  </si>
+  <si>
+    <t>1022415180</t>
+  </si>
+  <si>
+    <t>1022973517</t>
+  </si>
+  <si>
+    <t>1023026833</t>
+  </si>
+  <si>
+    <t>1023365940</t>
+  </si>
+  <si>
+    <t>1023866590</t>
+  </si>
+  <si>
+    <t>1024574799</t>
+  </si>
+  <si>
+    <t>1024591972</t>
+  </si>
+  <si>
+    <t>1026269702</t>
+  </si>
+  <si>
+    <t>1030595790</t>
+  </si>
+  <si>
+    <t>1030678228</t>
+  </si>
+  <si>
+    <t>1030687904</t>
+  </si>
+  <si>
+    <t>1031135783</t>
+  </si>
+  <si>
+    <t>1032677600</t>
+  </si>
+  <si>
+    <t>1032796079</t>
+  </si>
+  <si>
+    <t>1033685058</t>
+  </si>
+  <si>
+    <t>1033716719</t>
+  </si>
+  <si>
+    <t>1035230632</t>
+  </si>
+  <si>
+    <t>1043663400</t>
+  </si>
+  <si>
+    <t>1064556081</t>
+  </si>
+  <si>
+    <t>1069750848</t>
+  </si>
+  <si>
+    <t>1069832679</t>
+  </si>
+  <si>
+    <t>1073671678</t>
+  </si>
+  <si>
+    <t>1110538315</t>
+  </si>
+  <si>
+    <t>1128277446</t>
+  </si>
+  <si>
+    <t>1128450311</t>
+  </si>
+  <si>
+    <t>1232399996</t>
+  </si>
+  <si>
+    <t>70634903</t>
+  </si>
+  <si>
+    <t>41966389</t>
+  </si>
+  <si>
+    <t>74584166</t>
+  </si>
+  <si>
+    <t>61034044</t>
+  </si>
+  <si>
+    <t>46437661</t>
+  </si>
+  <si>
+    <t>76926152</t>
+  </si>
+  <si>
+    <t>9599394</t>
+  </si>
+  <si>
+    <t>41062576</t>
+  </si>
+  <si>
+    <t>09011527</t>
+  </si>
+  <si>
+    <t>007850201</t>
   </si>
 </sst>
 </file>
@@ -787,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -803,456 +1007,456 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>5115859</v>
+      <c r="A2" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>7215509</v>
+      <c r="A3" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>13958754</v>
+      <c r="A4" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>33223712</v>
+      <c r="A5" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>43182389</v>
+      <c r="A6" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>52359520</v>
+      <c r="A7" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>52360965</v>
+      <c r="A8" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>52937353</v>
+      <c r="A9" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>60856457</v>
+      <c r="A10" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>76566719</v>
+      <c r="A11" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>1000048809</v>
+      <c r="A12" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>1000268963</v>
+      <c r="A13" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>1000406210</v>
+      <c r="A14" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>1000691794</v>
+      <c r="A15" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>1000784663</v>
+      <c r="A16" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>1000873002</v>
+      <c r="A17" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>1001299432</v>
+      <c r="A18" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>1005180052</v>
+      <c r="A19" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>1006126137</v>
+      <c r="A20" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>1006187617</v>
+      <c r="A21" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>1006854586</v>
+      <c r="A22" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>1007437362</v>
+      <c r="A23" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>1007719161</v>
+      <c r="A24" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>1010207469</v>
+      <c r="A25" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>1010213899</v>
+      <c r="A26" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>1010231249</v>
+      <c r="A27" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>1012428710</v>
+      <c r="A28" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>1013677430</v>
+      <c r="A29" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>1016019099</v>
+      <c r="A30" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>1022328197</v>
+      <c r="A31" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>1022399552</v>
+      <c r="A32" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>1022415180</v>
+      <c r="A33" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>1022973517</v>
+      <c r="A34" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>1023026833</v>
+      <c r="A35" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>1023365940</v>
+      <c r="A36" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>1023866590</v>
+      <c r="A37" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>1024574799</v>
+      <c r="A38" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>1024591972</v>
+      <c r="A39" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>1026269702</v>
+      <c r="A40" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>1030595790</v>
+      <c r="A41" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
-        <v>1030678228</v>
+      <c r="A42" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="2">
-        <v>1030687904</v>
+      <c r="A43" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2">
-        <v>1031135783</v>
+      <c r="A44" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="2">
-        <v>1032677600</v>
+      <c r="A45" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>1032796079</v>
+      <c r="A46" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="2">
-        <v>1033685058</v>
+      <c r="A47" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="2">
-        <v>1033716719</v>
+      <c r="A48" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="2">
-        <v>1035230632</v>
+      <c r="A49" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="2">
-        <v>1043663400</v>
+      <c r="A50" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="2">
-        <v>1064556081</v>
+      <c r="A51" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="2">
-        <v>1069750848</v>
+      <c r="A52" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="2">
-        <v>1069832679</v>
+      <c r="A53" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="2">
-        <v>1073671678</v>
+      <c r="A54" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="2">
-        <v>1110538315</v>
+      <c r="A55" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>1128277446</v>
+      <c r="A56" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="2">
-        <v>1128450311</v>
+      <c r="A57" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="2">
-        <v>1232399996</v>
+      <c r="A58" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>33</v>
@@ -1267,83 +1471,88 @@
       </c>
     </row>
     <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>70634903</v>
+      <c r="A60" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="2">
-        <v>41966389</v>
+      <c r="A61" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="2">
-        <v>9011527</v>
+      <c r="A62" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="2">
-        <v>74584166</v>
+      <c r="A63" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="2">
-        <v>61034044</v>
+      <c r="A64" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="2">
-        <v>46437661</v>
+      <c r="A65" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>76926152</v>
+      <c r="A66" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="2">
-        <v>7850201</v>
+      <c r="A67" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
-        <v>9599394</v>
+      <c r="A68" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>41062576</v>
+      <c r="A69" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
